--- a/www/flightdata/xlsx/eoss-316.xlsx
+++ b/www/flightdata/xlsx/eoss-316.xlsx
@@ -3081,7 +3081,7 @@
         <v>33012.89</v>
       </c>
       <c r="I2">
-        <v>515</v>
+        <v>377</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
